--- a/data/trans_orig/IP07KS_C08_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C08_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de divertirse con sus amigos/as en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según la frecuencia de divertirse con sus amigos/as, percibida por el/la menor en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,69 +725,69 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>657</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>43,12%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>513</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43056</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31412</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>49586</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>79,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28448</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8522</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52871</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>29734</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>22316</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52767</t>
+          <t>34106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73522</t>
+          <t>72790</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99901</t>
+          <t>81292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11036</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>32692</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8165</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>52938</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>52,85%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>45083</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82670</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>298</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17288</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13629</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19979</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,57%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>19163</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16516</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20477</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>79,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>38353</t>
+          <t>36490</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33444</t>
+          <t>31077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41953</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7722</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1706</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4353</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8669</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -2310,82 +2310,82 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5116</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>20,13%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,74 +2766,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1895</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>71,53%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>382</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>14899</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11599</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>17381</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>57,18%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>85,68%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>11745</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8362</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>13543</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>56,89%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>14458</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4756</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2329</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>8316</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>23,45%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>2953</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>6336</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>43,11%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -3787,82 +3787,82 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>630</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>13627</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>9047</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>16394</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>70,06%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>46,51%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>84,28%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>15371</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>11838</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>17222</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>83,43%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>93,47%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>18115</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>24464</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>34080</t>
+          <t>33480</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>4170</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>9191</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>4905</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>26,62%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -4469,82 +4469,82 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2608</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>479</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>38629</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>28766</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>43804</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>60,49%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>92,11%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>22915</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>18496</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>25554</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>83,95%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>67,76%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>93,62%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>27512</t>
+          <t>19668</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>42638</t>
+          <t>27102</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>60459</t>
+          <t>62737</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>50632</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>68970</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -4925,107 +4925,107 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>7971</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2894</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>18717</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>39,36%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>4380</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>4736</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>1741</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>8799</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>32,24%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>7674</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>2709</t>
-        </is>
-      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>12707</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>25611</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>38,23%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>12055</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>6212</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>25189</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -5151,82 +5151,82 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>957</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>4570</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>957</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>27820</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>19529</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>36522</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>22,38%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>41,86%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>16918</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>11295</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>23750</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>37,4%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>18846</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>13143</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>42310</t>
+          <t>46666</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>36229</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>51888</t>
+          <t>57403</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>52681</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>43958</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>61220</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>60,38%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>50,38%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>70,17%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>44742</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>37643</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>50513</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>70,46%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>59,28%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>79,54%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>49591</t>
+          <t>49362</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>57542</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>94333</t>
+          <t>102043</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>83953</t>
+          <t>90669</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>104826</t>
+          <t>113067</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>6445</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2767</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>12810</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>14,68%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>1844</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>5186</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -5946,82 +5946,82 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>173407</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>157428</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>190120</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>64,2%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>58,29%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>70,39%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>117715</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>73170</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>140342</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>55,93%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>177040</t>
+          <t>123774</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>158353</t>
+          <t>111427</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>195529</t>
+          <t>135159</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>294755</t>
+          <t>297180</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>239604</t>
+          <t>273982</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>320608</t>
+          <t>317365</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>85097</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>69630</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>100837</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>88841</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>66360</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>134984</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>83959</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>66763</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>103297</t>
+          <t>81584</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>172800</t>
+          <t>154348</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>146293</t>
+          <t>133760</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>232921</t>
+          <t>176391</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>9226</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>4969</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>16137</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>3916</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>7979</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -6515,107 +6515,107 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>6066</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>467</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6628,82 +6628,82 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>1883</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>303</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>482619</t>
+          <t>467688</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
